--- a/docs/safe-check-sheet.xlsx
+++ b/docs/safe-check-sheet.xlsx
@@ -222,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -271,9 +271,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -700,7 +697,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2. 印刷前に「② 決められた準備金の額」だけは毎回同じ金額を入れておく。</t>
+          <t>2. 釣銭準備金は100,000円で固定(2,000円札は使わないため欄なし)。</t>
         </is>
       </c>
     </row>
@@ -905,12 +902,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>100円玉</t>
+          <t>50円玉</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="14">
-        <f>100*F8</f>
+        <f>50*F8</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -928,12 +925,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>50円玉</t>
+          <t>10円玉</t>
         </is>
       </c>
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="14">
-        <f>50*F9</f>
+        <f>10*F9</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -941,22 +938,22 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2,000円札</t>
+          <t>1,000円札</t>
         </is>
       </c>
       <c r="B10" s="13" t="n"/>
       <c r="C10" s="14">
-        <f>2000*B10</f>
+        <f>1000*B10</f>
         <v/>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>10円玉</t>
+          <t>5円玉</t>
         </is>
       </c>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="14">
-        <f>10*F10</f>
+        <f>5*F10</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -964,22 +961,22 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>1,000円札</t>
+          <t>500円玉</t>
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14">
-        <f>1000*B11</f>
+        <f>500*B11</f>
         <v/>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>5円玉</t>
+          <t>1円玉</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="14">
-        <f>5*F11</f>
+        <f>1*F11</f>
         <v/>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -987,25 +984,14 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>500円玉</t>
+          <t>100円玉</t>
         </is>
       </c>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="14">
-        <f>500*B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>1円玉</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14">
-        <f>1*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="n"/>
+        <f>100*B12</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -1021,7 +1007,7 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>②は毎回同じ金額。事前に決めて印刷前に記入しておく。
+          <t>②は100,000円で固定。
 ③が0でなければ「4. 差額があったとき」を必ず記入。</t>
         </is>
       </c>
@@ -1037,9 +1023,11 @@
       </c>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="H15" s="22" t="n"/>
+      <c r="D15" s="16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -1049,14 +1037,14 @@
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="23">
-        <f>IF(D15="","",D14-D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="26" t="n"/>
+      <c r="D16" s="22">
+        <f>IF(COUNT(B8:B12,F8:F11)=0,"",D14-D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -1073,56 +1061,56 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>案件名</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>区分
 売上/預り</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>受取日</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>帳簿の金額</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>実際の金額</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>差額</t>
         </is>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>銀行
 入金済</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>入金日/返却日</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="31">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30">
         <f>IF(OR(D20="",E20=""),"",E20-D20)</f>
         <v/>
       </c>
@@ -1131,15 +1119,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H20" s="29" t="n"/>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="31">
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30">
         <f>IF(OR(D21="",E21=""),"",E21-D21)</f>
         <v/>
       </c>
@@ -1148,15 +1136,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H21" s="29" t="n"/>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="31">
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30">
         <f>IF(OR(D22="",E22=""),"",E22-D22)</f>
         <v/>
       </c>
@@ -1165,15 +1153,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H22" s="29" t="n"/>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30">
         <f>IF(OR(D23="",E23=""),"",E23-D23)</f>
         <v/>
       </c>
@@ -1182,15 +1170,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H23" s="29" t="n"/>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="31">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30">
         <f>IF(OR(D24="",E24=""),"",E24-D24)</f>
         <v/>
       </c>
@@ -1199,15 +1187,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H24" s="29" t="n"/>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="31">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30">
         <f>IF(OR(D25="",E25=""),"",E25-D25)</f>
         <v/>
       </c>
@@ -1216,15 +1204,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H25" s="29" t="n"/>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="28" t="n"/>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="31">
+      <c r="A26" s="27" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30">
         <f>IF(OR(D26="",E26=""),"",E26-D26)</f>
         <v/>
       </c>
@@ -1233,15 +1221,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H26" s="29" t="n"/>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="31">
+      <c r="A27" s="27" t="n"/>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30">
         <f>IF(OR(D27="",E27=""),"",E27-D27)</f>
         <v/>
       </c>
@@ -1250,7 +1238,7 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H27" s="29" t="n"/>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -1268,11 +1256,11 @@
         <f>SUM(E20:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="22">
         <f>IF(COUNT(E20:E27)=0,"",E28-D28)</f>
         <v/>
       </c>
-      <c r="G28" s="32" t="n"/>
+      <c r="G28" s="31" t="n"/>
       <c r="H28" s="6" t="n"/>
     </row>
     <row r="30">
@@ -1290,7 +1278,7 @@
       <c r="H30" s="6" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>□ 受取日から7日以上たっている売上金はない(あれば今日入金する)</t>
         </is>
@@ -1300,7 +1288,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="6" t="n"/>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1308,7 +1296,7 @@
       <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>□ 預かり金の返却・精算の期限を過ぎているものはない</t>
         </is>
@@ -1318,7 +1306,7 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1326,7 +1314,7 @@
       <c r="H32" s="6" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>□ 封筒すべてに案件名・金額・受取者名が書いてある</t>
         </is>
@@ -1336,7 +1324,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="34" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1344,7 +1332,7 @@
       <c r="H33" s="6" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>□ 前回のチェック表の差額・対応事項はすべて解決している</t>
         </is>
@@ -1354,7 +1342,7 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="6" t="n"/>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="G34" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1362,7 +1350,7 @@
       <c r="H34" s="6" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>□ 金庫の鍵・暗証番号は決められた人だけが管理している</t>
         </is>
@@ -1372,7 +1360,7 @@
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="6" t="n"/>
-      <c r="G35" s="34" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1380,7 +1368,7 @@
       <c r="H35" s="6" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>□ チェック後に金庫を施錠し、2人で施錠を確認した</t>
         </is>
@@ -1390,7 +1378,7 @@
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="6" t="n"/>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G36" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -1417,7 +1405,7 @@
           <t>考えられる原因</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n"/>
+      <c r="B39" s="34" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
@@ -1431,7 +1419,7 @@
           <t>対応内容</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
+      <c r="B40" s="34" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="5" t="n"/>
       <c r="E40" s="5" t="n"/>
@@ -1445,7 +1433,7 @@
           <t>責任者への報告</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n"/>
+      <c r="B41" s="34" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
       <c r="E41" s="5" t="n"/>
@@ -1454,8 +1442,7 @@
       <c r="H41" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="G12:H12"/>
+  <mergeCells count="37">
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B3:C3"/>
@@ -1667,14 +1654,14 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>100円玉</t>
+          <t>50円玉</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G8" s="14">
-        <f>100*F8</f>
+        <f>50*F8</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -1694,14 +1681,14 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>50円玉</t>
+          <t>10円玉</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G9" s="14">
-        <f>50*F9</f>
+        <f>10*F9</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -1709,26 +1696,26 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>2,000円札</t>
+          <t>1,000円札</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C10" s="14">
-        <f>2000*B10</f>
+        <f>1000*B10</f>
         <v/>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>10円玉</t>
+          <t>5円玉</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G10" s="14">
-        <f>10*F10</f>
+        <f>5*F10</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -1736,26 +1723,26 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>1,000円札</t>
+          <t>500円玉</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C11" s="14">
-        <f>1000*B11</f>
+        <f>500*B11</f>
         <v/>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>5円玉</t>
+          <t>1円玉</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G11" s="14">
-        <f>5*F11</f>
+        <f>1*F11</f>
         <v/>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -1763,29 +1750,16 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>500円玉</t>
+          <t>100円玉</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C12" s="14">
-        <f>500*B12</f>
-        <v/>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>1円玉</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" s="14">
-        <f>1*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="n"/>
+        <f>100*B12</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -1801,7 +1775,7 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>②は毎回同じ金額。事前に決めて印刷前に記入しておく。
+          <t>②は100,000円で固定。
 ③が0でなければ「4. 差額があったとき」を必ず記入。</t>
         </is>
       </c>
@@ -1817,11 +1791,11 @@
       </c>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6" t="n"/>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="16" t="n">
         <v>100000</v>
       </c>
-      <c r="E15" s="21" t="n"/>
-      <c r="H15" s="22" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -1831,14 +1805,14 @@
       </c>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="23">
-        <f>IF(D15="","",D14-D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="26" t="n"/>
+      <c r="D16" s="22">
+        <f>IF(COUNT(B8:B12,F8:F11)=0,"",D14-D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -1855,72 +1829,72 @@
       <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>案件名</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>区分
 売上/預り</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>受取日</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>帳簿の金額</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>実際の金額</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>差額</t>
         </is>
       </c>
-      <c r="G19" s="27" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>銀行
 入金済</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>入金日/返却日</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>A社 周年パーティー</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>売上</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>10/02</t>
         </is>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="29" t="n">
         <v>180000</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="29" t="n">
         <v>180000</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <f>IF(OR(D20="",E20=""),"",E20-D20)</f>
         <v/>
       </c>
@@ -1929,31 +1903,31 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H20" s="29" t="inlineStr"/>
+      <c r="H20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>B様 結婚式二次会</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>預り</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>10/03</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="29" t="n">
         <v>50000</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="29" t="n">
         <v>49000</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="30">
         <f>IF(OR(D21="",E21=""),"",E21-D21)</f>
         <v/>
       </c>
@@ -1962,15 +1936,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr"/>
+      <c r="H21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="31">
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30">
         <f>IF(OR(D22="",E22=""),"",E22-D22)</f>
         <v/>
       </c>
@@ -1979,15 +1953,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H22" s="29" t="n"/>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31">
+      <c r="A23" s="27" t="n"/>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30">
         <f>IF(OR(D23="",E23=""),"",E23-D23)</f>
         <v/>
       </c>
@@ -1996,15 +1970,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H23" s="29" t="n"/>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="31">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30">
         <f>IF(OR(D24="",E24=""),"",E24-D24)</f>
         <v/>
       </c>
@@ -2013,15 +1987,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H24" s="29" t="n"/>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="31">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30">
         <f>IF(OR(D25="",E25=""),"",E25-D25)</f>
         <v/>
       </c>
@@ -2030,15 +2004,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H25" s="29" t="n"/>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="28" t="n"/>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="31">
+      <c r="A26" s="27" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30">
         <f>IF(OR(D26="",E26=""),"",E26-D26)</f>
         <v/>
       </c>
@@ -2047,15 +2021,15 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H26" s="29" t="n"/>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="31">
+      <c r="A27" s="27" t="n"/>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30">
         <f>IF(OR(D27="",E27=""),"",E27-D27)</f>
         <v/>
       </c>
@@ -2064,7 +2038,7 @@
           <t>□</t>
         </is>
       </c>
-      <c r="H27" s="29" t="n"/>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
@@ -2082,11 +2056,11 @@
         <f>SUM(E20:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="22">
         <f>IF(COUNT(E20:E27)=0,"",E28-D28)</f>
         <v/>
       </c>
-      <c r="G28" s="32" t="n"/>
+      <c r="G28" s="31" t="n"/>
       <c r="H28" s="6" t="n"/>
     </row>
     <row r="30">
@@ -2104,7 +2078,7 @@
       <c r="H30" s="6" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>□ 受取日から7日以上たっている売上金はない(あれば今日入金する)</t>
         </is>
@@ -2114,7 +2088,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="6" t="n"/>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2122,7 +2096,7 @@
       <c r="H31" s="6" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>□ 預かり金の返却・精算の期限を過ぎているものはない</t>
         </is>
@@ -2132,7 +2106,7 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="6" t="n"/>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2140,7 +2114,7 @@
       <c r="H32" s="6" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>□ 封筒すべてに案件名・金額・受取者名が書いてある</t>
         </is>
@@ -2150,7 +2124,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="34" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2158,7 +2132,7 @@
       <c r="H33" s="6" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>□ 前回のチェック表の差額・対応事項はすべて解決している</t>
         </is>
@@ -2168,7 +2142,7 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="6" t="n"/>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="G34" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2176,7 +2150,7 @@
       <c r="H34" s="6" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>□ 金庫の鍵・暗証番号は決められた人だけが管理している</t>
         </is>
@@ -2186,7 +2160,7 @@
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="6" t="n"/>
-      <c r="G35" s="34" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2194,7 +2168,7 @@
       <c r="H35" s="6" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>□ チェック後に金庫を施錠し、2人で施錠を確認した</t>
         </is>
@@ -2204,7 +2178,7 @@
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="6" t="n"/>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G36" s="33" t="inlineStr">
         <is>
           <t>はい ・ いいえ</t>
         </is>
@@ -2231,7 +2205,7 @@
           <t>考えられる原因</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>B様預り金:当日のキャンセル料1,000円を現金で返金、記録漏れ</t>
         </is>
@@ -2249,7 +2223,7 @@
           <t>対応内容</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>B様への返金記録を追記し帳簿を修正。封筒に返金メモを同封</t>
         </is>
@@ -2267,7 +2241,7 @@
           <t>責任者への報告</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="34" t="inlineStr">
         <is>
           <t>10/05 19:00 田中店長へ口頭報告済み</t>
         </is>
@@ -2280,8 +2254,7 @@
       <c r="H41" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="G12:H12"/>
+  <mergeCells count="37">
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B3:C3"/>

--- a/docs/safe-check-sheet.xlsx
+++ b/docs/safe-check-sheet.xlsx
@@ -735,7 +735,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6. 100,000円を超えた分は銀行へ入金、足りない分は補充して、金庫を毎週100,000円に戻す。</t>
+          <t>6. 150,000円を超えた分は銀行へ入金、足りない分は補充して、金庫を毎週150,000円に戻す。</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="8" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="9" t="inlineStr">
@@ -1320,7 +1320,7 @@
       <c r="E36" s="24" t="inlineStr">
         <is>
           <t>・⑥が0でなければ下の「差額の原因」を記入し、当日中に責任者へ報告
-・⑨は必ず100,000円になる。来週の用紙の「繰越」は印字済み
+・⑨は必ず150,000円になる。来週の用紙の「繰越」は印字済み
 ・銀行へ入金したら、その控えをこの用紙に貼る</t>
         </is>
       </c>
@@ -1408,7 +1408,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>⑦ 銀行へ入金(⑤が100,000円を超えた分)</t>
+          <t>⑦ 銀行へ入金(⑤が150,000円を超えた分)</t>
         </is>
       </c>
       <c r="B42" s="17" t="n"/>
@@ -1421,7 +1421,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>⑧ 補充(⑤が100,000円に足りない分)</t>
+          <t>⑧ 補充(⑤が150,000円に足りない分)</t>
         </is>
       </c>
       <c r="B43" s="17" t="n"/>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="8" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="9" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B29" s="21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C29" s="22">
         <f>10000*B29</f>
@@ -2201,7 +2201,7 @@
       <c r="E36" s="24" t="inlineStr">
         <is>
           <t>・⑥が0でなければ下の「差額の原因」を記入し、当日中に責任者へ報告
-・⑨は必ず100,000円になる。来週の用紙の「繰越」は印字済み
+・⑨は必ず150,000円になる。来週の用紙の「繰越」は印字済み
 ・銀行へ入金したら、その控えをこの用紙に貼る</t>
         </is>
       </c>
@@ -2289,7 +2289,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>⑦ 銀行へ入金(⑤が100,000円を超えた分)</t>
+          <t>⑦ 銀行へ入金(⑤が150,000円を超えた分)</t>
         </is>
       </c>
       <c r="B42" s="17" t="n"/>
@@ -2304,7 +2304,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>⑧ 補充(⑤が100,000円に足りない分)</t>
+          <t>⑧ 補充(⑤が150,000円に足りない分)</t>
         </is>
       </c>
       <c r="B43" s="17" t="n"/>

--- a/docs/safe-check-sheet.xlsx
+++ b/docs/safe-check-sheet.xlsx
@@ -682,14 +682,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>・紙には書かず、スマホのフォーム「金庫 現金の出し入れ登録」から登録する。</t>
+          <t>・紙には書かず、スマホのフォーム(大阪GB 現金出納帳)から登録する。処理区分は5つから選ぶ。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>・売上封筒には、フォーム登録後に届く記録ID(U0001など)・案件名・金額・受取日を書く。</t>
+          <t>・売上封筒には、受取日・相手先・金額・担当者を書く。銀行へ行くときは封筒を全部入金する。</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1. 月曜朝に届くメール「【金庫確認】今あるはずの金額」の数字を、この表の青い欄に書き写す。</t>
+          <t>1. 月曜朝に届くメール「【金庫確認】あるはずの金額」の数字を、この表の青い欄に書き写す。</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>青い欄は、月曜朝の「【金庫確認】今あるはずの金額」メールから書き写してから数える。黄色の欄は数えた結果を書く。</t>
+          <t>青い欄は、月曜朝の「【金庫確認】あるはずの金額」メール(または「現金残高」シート)から書き写してから数える。黄色の欄は数えた結果を書く。</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>記録ID</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>案件名</t>
+          <t>相手先</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
@@ -1169,7 +1169,9 @@
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="20" t="n"/>
+      <c r="A25" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="B25" s="20" t="n"/>
       <c r="C25" s="21" t="n"/>
       <c r="D25" s="7" t="n"/>
@@ -1186,7 +1188,9 @@
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="20" t="n"/>
+      <c r="A26" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="B26" s="20" t="n"/>
       <c r="C26" s="21" t="n"/>
       <c r="D26" s="7" t="n"/>
@@ -1203,7 +1207,9 @@
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="20" t="n"/>
+      <c r="A27" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="B27" s="20" t="n"/>
       <c r="C27" s="21" t="n"/>
       <c r="D27" s="7" t="n"/>
@@ -1220,7 +1226,9 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="20" t="n"/>
+      <c r="A28" s="16" t="n">
+        <v>4</v>
+      </c>
       <c r="B28" s="20" t="n"/>
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="7" t="n"/>
@@ -1237,7 +1245,9 @@
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="20" t="n"/>
+      <c r="A29" s="16" t="n">
+        <v>5</v>
+      </c>
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="21" t="n"/>
       <c r="D29" s="7" t="n"/>
@@ -1254,7 +1264,9 @@
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="20" t="n"/>
+      <c r="A30" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="B30" s="20" t="n"/>
       <c r="C30" s="21" t="n"/>
       <c r="D30" s="7" t="n"/>
@@ -1271,7 +1283,9 @@
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="20" t="n"/>
+      <c r="A31" s="16" t="n">
+        <v>7</v>
+      </c>
       <c r="B31" s="20" t="n"/>
       <c r="C31" s="21" t="n"/>
       <c r="D31" s="7" t="n"/>
@@ -1288,7 +1302,9 @@
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="20" t="n"/>
+      <c r="A32" s="16" t="n">
+        <v>8</v>
+      </c>
       <c r="B32" s="20" t="n"/>
       <c r="C32" s="21" t="n"/>
       <c r="D32" s="7" t="n"/>
@@ -1356,7 +1372,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>今あるはずの金額(メールの1行目)</t>
+          <t>あるはずの合計(メールの1行目)</t>
         </is>
       </c>
       <c r="B37" s="23" t="n"/>
@@ -1404,7 +1420,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>□ すべての封筒に 記録ID・案件名・金額・受取日 が書いてある</t>
+          <t>□ すべての封筒に 受取日・相手先・金額・担当者 が書いてある</t>
         </is>
       </c>
       <c r="B42" s="23" t="n"/>
@@ -1608,7 +1624,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>青い欄は、月曜朝の「【金庫確認】今あるはずの金額」メールから書き写してから数える。黄色の欄は数えた結果を書く。</t>
+          <t>青い欄は、月曜朝の「【金庫確認】あるはずの金額」メール(または「現金残高」シート)から書き写してから数える。黄色の欄は数えた結果を書く。</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1976,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>記録ID</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1970,7 +1986,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>案件名</t>
+          <t>相手先</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
@@ -1996,10 +2012,8 @@
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>U0001</t>
-        </is>
+      <c r="A25" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
@@ -2029,10 +2043,8 @@
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>U0002</t>
-        </is>
+      <c r="A26" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
@@ -2062,7 +2074,9 @@
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="20" t="n"/>
+      <c r="A27" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="B27" s="20" t="n"/>
       <c r="C27" s="21" t="n"/>
       <c r="D27" s="7" t="n"/>
@@ -2079,7 +2093,9 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="20" t="n"/>
+      <c r="A28" s="16" t="n">
+        <v>4</v>
+      </c>
       <c r="B28" s="20" t="n"/>
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="7" t="n"/>
@@ -2096,7 +2112,9 @@
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="20" t="n"/>
+      <c r="A29" s="16" t="n">
+        <v>5</v>
+      </c>
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="21" t="n"/>
       <c r="D29" s="7" t="n"/>
@@ -2113,7 +2131,9 @@
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="20" t="n"/>
+      <c r="A30" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="B30" s="20" t="n"/>
       <c r="C30" s="21" t="n"/>
       <c r="D30" s="7" t="n"/>
@@ -2130,7 +2150,9 @@
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="20" t="n"/>
+      <c r="A31" s="16" t="n">
+        <v>7</v>
+      </c>
       <c r="B31" s="20" t="n"/>
       <c r="C31" s="21" t="n"/>
       <c r="D31" s="7" t="n"/>
@@ -2147,7 +2169,9 @@
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="20" t="n"/>
+      <c r="A32" s="16" t="n">
+        <v>8</v>
+      </c>
       <c r="B32" s="20" t="n"/>
       <c r="C32" s="21" t="n"/>
       <c r="D32" s="7" t="n"/>
@@ -2215,7 +2239,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>今あるはずの金額(メールの1行目)</t>
+          <t>あるはずの合計(メールの1行目)</t>
         </is>
       </c>
       <c r="B37" s="23" t="n"/>
@@ -2265,7 +2289,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>□ すべての封筒に 記録ID・案件名・金額・受取日 が書いてある</t>
+          <t>□ すべての封筒に 受取日・相手先・金額・担当者 が書いてある</t>
         </is>
       </c>
       <c r="B42" s="23" t="n"/>

--- a/docs/safe-check-sheet.xlsx
+++ b/docs/safe-check-sheet.xlsx
@@ -751,7 +751,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>・売上封筒のお金を、支払いや金庫金の補充に使わない。</t>
+          <t>・売上封筒のお金で直接支払わない。金庫金へ移すときは「振替(売上封筒から金庫金へ)」で登録する。</t>
         </is>
       </c>
     </row>
@@ -847,6 +847,7 @@
         <is>
           <t>・ポーチは1個ずつ数え、1万円ちょうどか確認する
 ・現場に持ち出し中のポーチは「持出中」と書き、戻ったら数える
+・1万円を超えた分は売上封筒へ、足りない分は原因を確認
 ・ポーチのお金を支払いに使わない</t>
         </is>
       </c>
@@ -1660,6 +1661,7 @@
         <is>
           <t>・ポーチは1個ずつ数え、1万円ちょうどか確認する
 ・現場に持ち出し中のポーチは「持出中」と書き、戻ったら数える
+・1万円を超えた分は売上封筒へ、足りない分は原因を確認
 ・ポーチのお金を支払いに使わない</t>
         </is>
       </c>

--- a/docs/safe-check-sheet.xlsx
+++ b/docs/safe-check-sheet.xlsx
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>・売上封筒: ケータリング・オードブルの現金売上。茶封筒に入れて保管し、全額を銀行へ入金する。</t>
+          <t>・売上封筒: ケータリング・オードブルの現金売上。茶封筒に入れて保管する。入金の日に小銭と補充分を金庫金へ振替し、残りのお札を入金する。</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>・売上封筒には、受取日・相手先・金額・担当者を書く。銀行へ行くときは封筒を全部入金する。</t>
+          <t>・売上封筒には、受取日・相手先・金額・担当者を書く。支払いには使わない。</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>□ 売上封筒のお金を支払いや補充に使っていない</t>
+          <t>□ 売上封筒から金庫金へ移したお金は、すべて「振替」で登録してある</t>
         </is>
       </c>
       <c r="B44" s="23" t="n"/>
@@ -2327,7 +2327,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>□ 売上封筒のお金を支払いや補充に使っていない</t>
+          <t>□ 売上封筒から金庫金へ移したお金は、すべて「振替」で登録してある</t>
         </is>
       </c>
       <c r="B44" s="23" t="n"/>
